--- a/AAII_Financials/Quarterly/PCAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PCAR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
   <si>
     <t>PCAR</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7546700</v>
+      </c>
+      <c r="E8" s="3">
         <v>6776500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6820800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6671800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7510500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7441700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7907500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8239900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8772100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8744300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9076600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8696400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8881100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8473300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8129500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7058900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7158700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6472600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>6686100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5146800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>11689400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5845500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5568600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4936000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3062200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5161700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6117200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6367000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6627900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6487600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6279700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5756800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5805200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>5654000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>5454600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>5059700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>4704200</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>4237900</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>4070700</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>4249000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5989000</v>
+      </c>
+      <c r="E9" s="3">
         <v>5416500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5504900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5345400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5995400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5891000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6195800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6427700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6772300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6673800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6922700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6626700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6851700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6493100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6505200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5689300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5811000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5285500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5567100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4176200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9349100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4690700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4487000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3958300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2441500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4188400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4890000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5106800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>5341900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>5216900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>5089000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4654700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>4647300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>4534300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>4444600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>4079700</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>3781200</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>3373800</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>3293400</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>3406400</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1132100</v>
+      </c>
+      <c r="E10" s="3">
         <v>933300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>862100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>887300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1090600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1143800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1271400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1382600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1601200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1675100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1782100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1739400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1734300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1705800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1624300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1369600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1347700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1187100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1119000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>970600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2340300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1154800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1081600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>977700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>620700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>973300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1227200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1260200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1286000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1270700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1190700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1102100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1157900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1119700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1010000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>980000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>923000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>864100</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>777300</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>842600</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,130 +1248,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>114300</v>
+      </c>
+      <c r="E12" s="3">
         <v>109100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>106200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>111000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>112900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>115400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>115300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>115000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>117100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>105500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>108900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>103500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>101300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>97200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>99900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>82900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>80400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>78000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>87100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>72500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>164500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>80100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>71700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>64700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>66500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>71000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>83600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>82200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>82500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>78300</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>80500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>72900</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>76700</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>76000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>70600</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>67000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>66100</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>61000</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>67600</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>59200</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1479,31 +1496,34 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="3">
         <v>2000</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="3">
         <v>350000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-14000</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>10</v>
@@ -1511,20 +1531,20 @@
       <c r="L14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>10</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q14" s="3">
         <v>600000</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>10</v>
@@ -1532,8 +1552,8 @@
       <c r="S14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1583,8 +1603,8 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
-      <c r="AK14" s="3" t="s">
-        <v>10</v>
+      <c r="AK14" s="3">
+        <v>0</v>
       </c>
       <c r="AL14" s="3" t="s">
         <v>10</v>
@@ -1592,139 +1612,145 @@
       <c r="AM14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AN14" s="3">
-        <v>0</v>
+      <c r="AN14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AO14" s="3">
         <v>0</v>
       </c>
-      <c r="AP14" s="3" t="s">
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>103500</v>
+      </c>
+      <c r="E15" s="3">
         <v>88100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>89400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>90300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>90900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>86800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>86300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>94300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>96500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>95100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>119900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>111700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>106000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>97700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>134500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>137400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>145400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>143500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>190400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>219800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>559200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>278700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>292000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>262500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>224100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>229400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>241900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>195300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>183600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>177400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>177600</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>178500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>185500</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>186400</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>188800</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>186200</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>172800</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>179700</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>165300</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>162600</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>6077200</v>
+        <v>6639300</v>
       </c>
       <c r="E17" s="3">
+        <v>6073600</v>
+      </c>
+      <c r="F17" s="3">
         <v>6192700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6009900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6645500</v>
       </c>
-      <c r="H17" s="3">
-        <v>6540100</v>
-      </c>
       <c r="I17" s="3">
+        <v>6531100</v>
+      </c>
+      <c r="J17" s="3">
         <v>6875900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7093000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7405600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7296800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7535200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7179900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7370100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6999100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6936100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6079800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6218000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5690900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6024600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4637100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10401500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5214300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5017400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4420300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2859800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4670300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5402300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5562500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5785300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5644200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5514900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5062800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5071600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4969600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>4852900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>4478300</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>4163300</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>3760800</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>3665200</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>3765000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>699300</v>
+        <v>907400</v>
       </c>
       <c r="E18" s="3">
+        <v>702900</v>
+      </c>
+      <c r="F18" s="3">
         <v>628100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>661900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>865000</v>
       </c>
-      <c r="H18" s="3">
-        <v>901600</v>
-      </c>
       <c r="I18" s="3">
+        <v>910600</v>
+      </c>
+      <c r="J18" s="3">
         <v>1031600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1146900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1366500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1447500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1541400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1516500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1511000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1474200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1193400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>979100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>940700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>781700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>661500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>509700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1287900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>631200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>551200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>515700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>202400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>491400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>714900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>804500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>842600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>843400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>764800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>694000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>733600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>684400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>601700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>581400</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>540900</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>477100</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>405500</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>484000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,357 +2085,364 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E20" s="3">
         <v>16700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>6000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>17800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>12400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-24700</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-300</v>
       </c>
       <c r="K20" s="3">
         <v>-300</v>
       </c>
       <c r="L20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M20" s="3">
         <v>-1100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-8100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-700</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>56400</v>
       </c>
       <c r="R20" s="3">
         <v>56400</v>
       </c>
       <c r="S20" s="3">
+        <v>56400</v>
+      </c>
+      <c r="T20" s="3">
         <v>27800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>29500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>35000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>12800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>40300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>18100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>14200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>19400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>28500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>39200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>27500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>41000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>30300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>35600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>44500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>24300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>40600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>25800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>2600</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>400</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-1900</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-28900</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>13400</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>770700</v>
+        <v>1015800</v>
       </c>
       <c r="E21" s="3">
+        <v>774300</v>
+      </c>
+      <c r="F21" s="3">
         <v>716100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>746200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>938100</v>
       </c>
-      <c r="H21" s="3">
-        <v>976000</v>
-      </c>
       <c r="I21" s="3">
+        <v>985000</v>
+      </c>
+      <c r="J21" s="3">
         <v>1142600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1241500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1463300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1543700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1669400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1627300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1616300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1572600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1454400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1238500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1165400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>996900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>907500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>732400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1810600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>901000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>834900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>801300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>472200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>802600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1027300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1117600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1134100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1138100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1069000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>970900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1042500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>983700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>897500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>867900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>808000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>707400</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>666400</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>745100</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>10</v>
+      <c r="D22" s="3">
+        <v>16800</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="3">
         <v>3100</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J22" s="3">
         <v>25700</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="K22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1800</v>
       </c>
-      <c r="L22" s="3" t="s">
+      <c r="M22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>7900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>7000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>4500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>4900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>74300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>55800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>46400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>39800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>36000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>35300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>79600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>42000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>43600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>45200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>46900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>68400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>54600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>67900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>58500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>59600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>56900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>49500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>54600</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>40800</v>
       </c>
-      <c r="AK22" s="3">
-        <v>0</v>
-      </c>
       <c r="AL22" s="3">
         <v>0</v>
       </c>
@@ -2418,252 +2458,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>981500</v>
+      </c>
+      <c r="E23" s="3">
         <v>776300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>704900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>743600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>931900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>643100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1149300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1256300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1460800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1534500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1641300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1589400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1568500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>919000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1175500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>979700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>922100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>771400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>660500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>487200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1248600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>607300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>521800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>489900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>184000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>462200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>687800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>777600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>814400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>819400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>752400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>668800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>719600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>669400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>604300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>581800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>539000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>448200</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>418900</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>494900</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>229500</v>
+      </c>
+      <c r="E24" s="3">
         <v>171000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>148000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>153600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>208100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>138000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>277300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>284200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>338200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>339200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>224000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>360900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>347400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>185100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>254200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>210300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>201700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>170900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>141800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>106700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>282300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>137200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>116000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>104400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>36300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>102800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>156500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>169700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>194700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>190400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>174300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>123500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>160000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>157300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>188500</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>179100</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>166000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>137900</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>130100</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>148700</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>752000</v>
+      </c>
+      <c r="E26" s="3">
         <v>605300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>556900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>590000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>723800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>505100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>872000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>972100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1122600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1195300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1417300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1228500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1221100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>733900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>921300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>769400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>720400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>600500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>518700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>380500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>966300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>470100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>405800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>385500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>147700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>359400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>531300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>607900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>619700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>629000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>578100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>545300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>559600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>512100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>415800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>402700</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>373000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>310300</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>288800</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>346200</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>752000</v>
+      </c>
+      <c r="E27" s="3">
         <v>605300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>556900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>590000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>723800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>505100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>872000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>972100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1122600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1195300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1417300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1228500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1221100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>733900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>921300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>769400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>720400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>600500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>518700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>380500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>966300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>470100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>405800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>385500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>147700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>359400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>531300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>607900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>619700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>629000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>578100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>545300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>559600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>512100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>415800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>402700</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>373000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>310300</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>288800</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>346200</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3236,8 +3297,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>10</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>10</v>
@@ -3254,11 +3315,11 @@
       <c r="AJ29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL29" s="3">
         <v>173400</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>10</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-16700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-6000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-17800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-12400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>24700</v>
-      </c>
-      <c r="J32" s="3">
-        <v>300</v>
       </c>
       <c r="K32" s="3">
         <v>300</v>
       </c>
       <c r="L32" s="3">
+        <v>300</v>
+      </c>
+      <c r="M32" s="3">
         <v>1100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>8100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>700</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-56400</v>
       </c>
       <c r="R32" s="3">
         <v>-56400</v>
       </c>
       <c r="S32" s="3">
+        <v>-56400</v>
+      </c>
+      <c r="T32" s="3">
         <v>-27800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-29500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-35000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-12800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-40300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-18100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-14200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-19400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-28500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-39200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-27500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-41000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-30300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-35600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-44500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-24300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-40600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-25800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-2600</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-400</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>1900</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>28900</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-13400</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-10900</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>752000</v>
+      </c>
+      <c r="E33" s="3">
         <v>605300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>556900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>590000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>723800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>505100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>872000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>972100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1122600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1195300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1417300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1228500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1221100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>733900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>921300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>769400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>720400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>600500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>518700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>380500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>966300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>470100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>405800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>385500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>147700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>359400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>531300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>607900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>619700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>629000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>578100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>545300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>559600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>512100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>589200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>402700</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>373000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>310300</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>288800</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>346200</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>752000</v>
+      </c>
+      <c r="E35" s="3">
         <v>605300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>556900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>590000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>723800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>505100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>872000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>972100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1122600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1195300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1417300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1228500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1221100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>733900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>921300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>769400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>720400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>600500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>518700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>380500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>966300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>470100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>405800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>385500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>147700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>359400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>531300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>607900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>619700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>629000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>578100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>545300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>559600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>512100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>589200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>402700</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>373000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>310300</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>288800</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>346200</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,175 +4305,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5407800</v>
+      </c>
+      <c r="E41" s="3">
         <v>5381900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6046000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6122100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5366000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5273500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6871100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6642100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5658300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5895800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6836700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5696900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4927900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4283300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4690900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3323500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3231300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3314900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3428300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2227800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3069800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3320000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3539600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3344300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3128000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3323100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4175100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3669500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3219400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2842600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3435900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2914000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2506800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2504100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2364700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2313300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1879800</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1764400</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1915700</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1787900</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3259600</v>
+      </c>
+      <c r="E42" s="3">
         <v>3213500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3207700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2946500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2913700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2826500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2778800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2510700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2145500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1831400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1822600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1743100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1690500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1638900</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4401,359 +4491,368 @@
         <v>0</v>
       </c>
       <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
         <v>1549400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1434600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1421100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1429000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1194300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1147200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1097000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1162100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1107800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1117300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1081600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1020400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1000300</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1033300</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1046500</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1367100</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1216000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>1244600</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>1206400</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>1140900</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>1078900</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2376300</v>
+      </c>
+      <c r="E43" s="3">
         <v>2256900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1981100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2090000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2210300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2212400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1933800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2199200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2731300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2410900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2198100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2303600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2350900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2347000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1919800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2018500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1959700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1927800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1575100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>12878200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>13425000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>13389500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>13018200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>12689200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>12381400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>12976800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>13392100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>13400700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>13315700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>13091900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>12155200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>12187600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>11732400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>11572700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>10825000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>10872500</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>10509900</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>10116600</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>9699600</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>10104200</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2384200</v>
+      </c>
+      <c r="E44" s="3">
         <v>2223400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2187500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2296900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2456700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2375600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2367100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2644800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2783000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2742600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2576700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2622400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2712900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2609200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2198800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2382100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2232200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2222100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1768300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2516700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2054600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1465400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1221900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1124500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1136400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1270100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1153200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1292600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1336600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1272600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1184700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1292000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1258500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1068300</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>928400</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>983000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>885300</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>772200</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>727800</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>824100</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>957800</v>
+      </c>
+      <c r="E45" s="3">
         <v>822800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>903900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1089400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>905500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>759700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>751200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>665900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>681500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>622400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>680600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>708900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>709300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>771200</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4767,115 +4866,118 @@
         <v>0</v>
       </c>
       <c r="V45" s="3">
+        <v>0</v>
+      </c>
+      <c r="W45" s="3">
         <v>667900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>796900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>572200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>515600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>541500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>492100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>529900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>388000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>387300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>403700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>401700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>364700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>376800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>492900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>396600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>404400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>252400</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>269900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>223900</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>225600</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>218300</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>34314900</v>
+      </c>
+      <c r="E46" s="3">
         <v>34002100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>34876200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>35257400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>34756500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>33900200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>34821600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>34686100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>32823900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>32055800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>32388900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>29877900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>28515900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>26537500</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4889,90 +4991,93 @@
         <v>0</v>
       </c>
       <c r="V46" s="3">
+        <v>0</v>
+      </c>
+      <c r="W46" s="3">
         <v>19840000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>20780900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>20168200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>19724300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>18893800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>18285100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>19196900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>20270500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>19857900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>19392700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>18690400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>18160900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>17770700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>17023900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>16588200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>15889600</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>15637200</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>14789500</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>14083500</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>13709600</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>14013400</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>367600</v>
+      </c>
+      <c r="E47" s="3">
         <v>373400</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="F47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>228100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>233300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>237600</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>10</v>
@@ -4995,24 +5100,24 @@
       <c r="P47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R47" s="3">
         <v>15406100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>14093400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>14208400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>14079100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>13480200</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
-      </c>
       <c r="W47" s="3">
         <v>0</v>
       </c>
@@ -5073,130 +5178,136 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4519800</v>
+      </c>
+      <c r="E48" s="3">
         <v>4518800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4621700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4442400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4397200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4127200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4122100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4123800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3997300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3909600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3975100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3760400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3765000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3687700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6271700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6053900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6323200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6516800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6587000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6591100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6737600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6674600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6864100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6572800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6448500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6433100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6569900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6273000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6297700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6146900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>6122500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>5988700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>5889800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>5974500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>6606400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>6473700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>6315600</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>5989700</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>5897800</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>5919900</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5317,8 +5428,11 @@
       <c r="AP49" s="3">
         <v>0</v>
       </c>
+      <c r="AQ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,53 +5678,56 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2441500</v>
+      </c>
+      <c r="E52" s="3">
         <v>2414600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2354900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1965300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2299200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2167000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1698100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2014900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1846900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1808300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1267100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1642300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1670600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1579300</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
@@ -5621,70 +5741,73 @@
         <v>0</v>
       </c>
       <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3">
         <v>1478800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1493700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1660600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1671600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1767100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1672800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1664700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1520700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1636800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1477800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1319700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1199000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1344000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1242100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1219000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>944200</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>993000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>948200</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>966500</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1031500</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1035600</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>43980100</v>
+      </c>
+      <c r="E54" s="3">
         <v>43553500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>44336200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>44201200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>44094800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>42724700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>43418900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>43281800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>41176600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>40373600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>40823400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>38039500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>36867700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>34826400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>33275500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>30623600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>30588700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>30586100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>29509400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>27909900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>29012200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>28503400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>28260000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>27233700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>26406400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>27294700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>28361100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>27767700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>27168200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>26157000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>25482400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>25103400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>24155800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>23781700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>23440200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>23103900</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>22053300</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>21039700</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>20638900</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>20968900</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,175 +6145,179 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4825700</v>
+      </c>
+      <c r="E57" s="3">
         <v>4761800</v>
       </c>
-      <c r="E57" s="3">
-        <v>2349700</v>
-      </c>
       <c r="F57" s="3">
+        <v>1455200</v>
+      </c>
+      <c r="G57" s="3">
         <v>4692200</v>
-      </c>
-      <c r="G57" s="3">
-        <v>4710400</v>
       </c>
       <c r="H57" s="3">
         <v>4710400</v>
       </c>
       <c r="I57" s="3">
-        <v>2699500</v>
+        <v>4710400</v>
       </c>
       <c r="J57" s="3">
+        <v>1598700</v>
+      </c>
+      <c r="K57" s="3">
         <v>4847300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4914200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5150400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1667600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4850200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5281400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5410100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5338500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5174500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5234000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5246300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4555400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4427900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4683700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4583800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3974900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3993600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3625000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3788700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3797200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4157200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>4052800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>4053700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3545800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3759500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>3611300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3526700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>3033200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>3228700</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>3009500</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>2763400</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>2426900</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>2670100</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>119900</v>
+      </c>
+      <c r="E58" s="3">
         <v>101700</v>
       </c>
-      <c r="E58" s="3">
-        <v>8387400</v>
-      </c>
       <c r="F58" s="3">
+        <v>8379900</v>
+      </c>
+      <c r="G58" s="3">
         <v>118500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>136300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>52900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5544700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>92900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>58200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>92000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5216800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>81500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>131600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>97000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6214,23 +6348,23 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-      <c r="AB58" s="3" t="s">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>500</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>900</v>
       </c>
       <c r="AE58" s="3">
         <v>900</v>
       </c>
       <c r="AF58" s="3">
+        <v>900</v>
+      </c>
+      <c r="AG58" s="3">
         <v>800</v>
-      </c>
-      <c r="AG58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AH58" s="3" t="s">
         <v>10</v>
@@ -6241,8 +6375,8 @@
       <c r="AJ58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AK58" s="3">
-        <v>0</v>
+      <c r="AK58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AL58" s="3">
         <v>0</v>
@@ -6259,55 +6393,58 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>333000</v>
+      </c>
+      <c r="E59" s="3">
         <v>339400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3905200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>447600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>463800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>392800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4603300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>392100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>378000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>391000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4845500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>387700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>88100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>67200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>974600</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>10</v>
@@ -6315,119 +6452,122 @@
       <c r="T59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V59" s="3">
         <v>521100</v>
-      </c>
-      <c r="V59" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="W59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X59" s="3">
-        <v>0</v>
+      <c r="X59" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Y59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="3">
         <v>242600</v>
       </c>
-      <c r="Z59" s="3">
-        <v>0</v>
-      </c>
       <c r="AA59" s="3">
         <v>0</v>
       </c>
       <c r="AB59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="3">
         <v>14300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>822000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>19200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>20100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>23200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>700200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>424600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>5200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>6700</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>13900</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>212600</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6217400</v>
+      </c>
+      <c r="E60" s="3">
         <v>6117600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>16083800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6196900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6384900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6284200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>14165200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6496400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6460000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6816000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>14062100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6398000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6535200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6452800</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6441,70 +6581,73 @@
         <v>0</v>
       </c>
       <c r="V60" s="3">
+        <v>0</v>
+      </c>
+      <c r="W60" s="3">
         <v>4427900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4683700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4583800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4217500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3993600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3625000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3803000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4619700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4177300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4073800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4077700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4246000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3764200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3613100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>3529900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>3457800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>3233900</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>3016200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2777300</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>2639500</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>2670800</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -6512,11 +6655,11 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>43900</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
@@ -6524,11 +6667,11 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>54400</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -6536,11 +6679,11 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>57100</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -6548,207 +6691,213 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>11471600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>10377900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>10564300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>10860000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>10431800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9855100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>10568600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>10564700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>10853800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>10392400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>10396600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>11138500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>11223200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>10856700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>10632800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>10197300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>9950500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>9586900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>9207700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>9130000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>8879400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>8832000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>8544100</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>8365500</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>8475200</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>8530300</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2209000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2197400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>733300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2244100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2310800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2235200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>512300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2056200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2056000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2101100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>874600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2133400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2114700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2036900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>624400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>587700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>581500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>620200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>590400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2296500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2576100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2637200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2798700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2663300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2608000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2715800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2812100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2771000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2826200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2776500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2693000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2581300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>2555600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>2554500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>3052500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>3102400</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>2992500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>2817600</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>2746600</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>2789600</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>23658800</v>
+      </c>
+      <c r="E66" s="3">
         <v>23796900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>25072200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>24832600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>25152200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>24702600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>25912000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>24618200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>23473700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>23501700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>24944600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>22016400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>21788400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>20944400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>20108400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>17730100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>18070700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>18442800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>17915400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>16579500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>17828400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>17785700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>17870000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>17049300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>16629600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>17657300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>18655000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>17805000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>17532800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>17051500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>16889500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>15932400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>15376400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>15214400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>15389700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>15168300</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>14552800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>13960400</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>13861300</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>13990700</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>19695100</v>
+      </c>
+      <c r="E72" s="3">
         <v>19127500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>18696100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>19049300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>18632800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>18082500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>17751000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>18613200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>17798600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>16833700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>15780300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>16182400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>15095500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>14005300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>13402400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>13760800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>13109900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>12507900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>12025800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>11998100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>11738700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>11364000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>11005200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>10953600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>10679100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>10642200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>10398500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>10798700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>10301800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9793100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9275400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9718400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>9271300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>8810100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>8369100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>8290700</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>7975900</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>7690900</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>7484900</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>7516700</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20321300</v>
+      </c>
+      <c r="E76" s="3">
         <v>19756600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>19264000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>19368600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>18942600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>18022100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>17506900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18663600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>17702900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16871900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>15878800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>16023100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15079300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13882000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13167100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12893500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12518000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12143300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11594000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11330400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>11183800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>10717700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>10390000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>10184400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>9776800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>9637400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>9706100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>9962700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>9635400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>9105500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>8592900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>9171000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>8779400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>8567300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>8050500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>7935600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>7500500</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>7079300</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>6777600</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>6978200</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>752000</v>
+      </c>
+      <c r="E81" s="3">
         <v>605300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>556900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>590000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>723800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>505100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>872000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>972100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1122600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1195300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1417300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1228500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1221100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>733900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>921300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>769400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>720400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>600500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>518700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>380500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>966300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>470100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>405800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>385500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>147700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>359400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>531300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>607900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>619700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>629000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>578100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>545300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>559600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>512100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>589200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>402700</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>373000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>310300</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>288800</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>346200</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>90900</v>
+      </c>
+      <c r="E83" s="3">
         <v>86800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>86300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>94300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>96500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>95100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>119900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>111700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>106000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>97700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>88900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>80300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>72900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>73200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>204600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>203000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>196900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>185700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>211000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>209900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>482400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>251700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>269500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>266200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>241300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>272000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>284900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>272100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>261200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>259100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>259700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>252600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>268300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>273500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>293200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>286100</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>269000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>259200</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>247500</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>250200</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>700800</v>
+      </c>
+      <c r="E89" s="3">
         <v>971800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1144300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1527800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>833400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>910300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1445700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1286200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>440000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1469000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1186700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1343000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>975500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>684800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1248800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>680700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>638200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>459300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1036500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>282500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>867700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>536900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>794700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>831700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>934900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>425900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>943700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>727100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>826500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>363000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1065100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>728700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>673200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>525300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>893300</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>637300</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>574700</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>610500</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>810300</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-158900</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-391800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-317900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-366300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-305600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-388900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-325800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-502900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-378100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-512800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-351800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-363400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-335700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-271600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-291800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-308700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-342500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-370700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-368600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-461000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-378500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-242400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-114600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-124200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-114000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-135800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-176400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-186800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-137300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-147100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-102800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-123100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-112900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-123200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-98400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-127500</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-107600</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-95600</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-429300</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-520600</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-525100</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-356800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-75000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-753800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-503300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-617500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-392600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1732000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1185500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1043700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-526100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-939900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-886400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-752000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-292700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-714500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-439500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-472900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-406100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-337300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-358700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-666700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-215700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-841500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-440200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-214300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-379800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-650900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-431100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-724700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-400700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-654200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-531300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-689100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-56100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-825100</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-369200</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-433300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-337000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-642900</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-135300</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>184300</v>
+      </c>
+      <c r="E96" s="3">
         <v>909400</v>
-      </c>
-      <c r="E96" s="3">
-        <v>173400</v>
       </c>
       <c r="F96" s="3">
         <v>173400</v>
       </c>
       <c r="G96" s="3">
+        <v>173400</v>
+      </c>
+      <c r="H96" s="3">
         <v>173300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1747000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>157400</v>
-      </c>
-      <c r="J96" s="3">
-        <v>157300</v>
       </c>
       <c r="K96" s="3">
         <v>157300</v>
       </c>
       <c r="L96" s="3">
+        <v>157300</v>
+      </c>
+      <c r="M96" s="3">
         <v>1816500</v>
-      </c>
-      <c r="M96" s="3">
-        <v>141300</v>
       </c>
       <c r="N96" s="3">
         <v>141300</v>
       </c>
       <c r="O96" s="3">
+        <v>141300</v>
+      </c>
+      <c r="P96" s="3">
         <v>130700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>1105300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-128800</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-118300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-118200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-639400</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-118100</v>
       </c>
       <c r="V96" s="3">
         <v>-118100</v>
       </c>
       <c r="W96" s="3">
+        <v>-118100</v>
+      </c>
+      <c r="X96" s="3">
         <v>-471800</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-353700</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-110900</v>
       </c>
       <c r="Z96" s="3">
         <v>-110900</v>
       </c>
       <c r="AA96" s="3">
+        <v>-110900</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-110600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-907400</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-110800</v>
       </c>
       <c r="AD96" s="3">
         <v>-110800</v>
       </c>
       <c r="AE96" s="3">
+        <v>-110800</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-110900</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-806100</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-97700</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-98100</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-98400</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-510100</v>
-      </c>
-      <c r="AK96" s="3">
-        <v>-87900</v>
       </c>
       <c r="AL96" s="3">
         <v>-87900</v>
       </c>
       <c r="AM96" s="3">
+        <v>-87900</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-87800</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-294700</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-84100</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-84200</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-406700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1551700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-394600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-262000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-291100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2134700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>643300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>812900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>300700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1880000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>942700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>358100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>492200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-690800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>723800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-72900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-189600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-156400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>507000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-738400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-651500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-508300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>179500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-209600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-944700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-833700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>172100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>193300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>268300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-550300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>134800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>214900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>60700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-339300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-24500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>138500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-62100</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-445700</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>8500</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>107400</v>
+      </c>
+      <c r="E101" s="3">
         <v>73900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-145400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>64100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-20000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-50100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>85900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-54300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>20100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>17900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>109300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-76100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-59300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>109300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-76100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-59300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-10200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-5700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-27400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-19300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-32500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>62600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>34400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>29000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-64400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>40700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-39200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>6700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-5300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-23800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-5100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-42100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>9500</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>7700</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>26900</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>36100</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>20900</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-48100</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>7400</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-70100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-663100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>754000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>32200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1543100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>211600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>977700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-323000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-987200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1275400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>760400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>735800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-280800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1367400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>92200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-83600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-113400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1200500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-842000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-469800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-219600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>195300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>216300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-195100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-852000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>505600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>450100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>376800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-593300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>521900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>407200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>2700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>139400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>51400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>433500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>115400</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-151300</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>127800</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-277000</v>
       </c>
     </row>
